--- a/sports_forms/023_volunteer_sports_official_application--sports_forms.xlsx
+++ b/sports_forms/023_volunteer_sports_official_application--sports_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'official',_'value':_'official'}</t>
+          <t>official</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Official', 'value': 'Official'}</t>
+          <t>Official</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'coach',_'value':_'coach'}</t>
+          <t>coach</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Coach', 'value': 'Coach'}</t>
+          <t>Coach</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'player',_'value':_'player'}</t>
+          <t>player</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Player', 'value': 'Player'}</t>
+          <t>Player</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'middle_school',_'value':_'middle_school'}</t>
+          <t>middle_school</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Middle School', 'value': 'middle_school'}</t>
+          <t>Middle School</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'college',_'value':_'college'}</t>
+          <t>college</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'College', 'value': 'college'}</t>
+          <t>College</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'basketball',_'value':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Basketball', 'value': 'basketball'}</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'soccer',_'value':_'soccer'}</t>
+          <t>soccer</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Soccer', 'value': 'soccer'}</t>
+          <t>Soccer</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'volleyball',_'value':_'volleyball'}</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Volleyball', 'value': 'volleyball'}</t>
+          <t>Volleyball</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'football',_'value':_'football'}</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Football', 'value': 'football'}</t>
+          <t>Football</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'completed_first_aid_training',_'value':_'completed_first_aid_training'}</t>
+          <t>completed_first_aid_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Completed First Aid Training', 'value': 'completed_first_aid_training'}</t>
+          <t>Completed First Aid Training</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_completed',_'value':_'not_completed_first_aid_training'}</t>
+          <t>not_completed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Completed', 'value': 'not_completed_first_aid_training'}</t>
+          <t>Not Completed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'unknown',_'value':_'unknown_first_aid_training'}</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Unknown', 'value': 'unknown_first_aid_training'}</t>
+          <t>Unknown</t>
         </is>
       </c>
     </row>
